--- a/output/pdf_financials_xlsx/MUR.xlsx
+++ b/output/pdf_financials_xlsx/MUR.xlsx
@@ -1356,31 +1356,31 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="17">
@@ -1405,13 +1405,13 @@
         <v>-0.007789</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.349359</v>
+        <v>-12.087329</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.107473</v>
+        <v>-7.171559</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.749794</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1662,13 +1662,13 @@
         <v>-0.795166</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5.868985</v>
+        <v>-5.868985</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.532043</v>
+        <v>-3.532043</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.874897</v>
+        <v>-0.874897</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="21">
@@ -1851,13 +1851,13 @@
         <v>-0.795166</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.868985</v>
+        <v>-5.868985</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.532043</v>
+        <v>-3.532043</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.874897</v>
+        <v>-0.874897</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -1865,31 +1865,31 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="24">
@@ -2058,10 +2058,10 @@
         <v>26.505533</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>97.816417</v>
+        <v>-97.816417</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>117.734767</v>
+        <v>-117.734767</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2074,22 +2074,22 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>23.59612</v>
+        <v>-23.59612</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>43.1766</v>
+        <v>-43.1766</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>49.019533</v>
+        <v>-49.019533</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>70.20350000000001</v>
+        <v>-70.20350000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>119.06825</v>
+        <v>-119.06825</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>203.400533</v>
+        <v>-203.400533</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="R26" s="3" t="n">
-        <v>12.848713</v>
+        <v>-12.848713</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>16.608818</v>
+        <v>-16.608818</v>
       </c>
     </row>
     <row r="27">
@@ -2139,31 +2139,31 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="28">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="30">
@@ -2411,13 +2411,13 @@
         <v>-0.9700419077034206</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>5.618199958059574</v>
+        <v>194.3818000419404</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.952947589734459</v>
+        <v>197.0470524102655</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6198,43 +6198,43 @@
         <v>3.824807</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>3.939945</v>
+        <v>4.176425</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.36583</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.684926</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.437644</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.840068</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.266467</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.745135</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.019705</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.876352</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.411789</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.188718</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.981348</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.669955</v>
       </c>
     </row>
     <row r="93">
@@ -10158,7 +10158,11 @@
           <t>Reserves (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11188,7 +11192,11 @@
           <t>Reserves (Notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12092,7 +12100,11 @@
           <t>Reserves (Notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12850,7 +12862,11 @@
           <t>Reserves (Notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -37549,13 +37565,13 @@
         </is>
       </c>
       <c r="J277" s="5" t="n">
-        <v>5.868985</v>
+        <v>-5.868985</v>
       </c>
       <c r="K277" s="5" t="n">
-        <v>3.532043</v>
+        <v>-3.532043</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>0.874897</v>
+        <v>-0.874897</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
@@ -37593,13 +37609,13 @@
         </is>
       </c>
       <c r="T277" s="5" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="U277" s="5" t="n">
-        <v>1.927307</v>
+        <v>-1.927307</v>
       </c>
       <c r="V277" s="5" t="n">
-        <v>1.82697</v>
+        <v>-1.82697</v>
       </c>
     </row>
     <row r="278">
@@ -40877,25 +40893,25 @@
         </is>
       </c>
       <c r="N309" s="5" t="n">
-        <v>1.179806</v>
+        <v>-1.179806</v>
       </c>
       <c r="O309" s="5" t="n">
-        <v>2.590596</v>
+        <v>-2.590596</v>
       </c>
       <c r="P309" s="5" t="n">
-        <v>1.470586</v>
+        <v>-1.470586</v>
       </c>
       <c r="Q309" s="5" t="n">
-        <v>2.106105</v>
+        <v>-2.106105</v>
       </c>
       <c r="R309" s="5" t="n">
-        <v>4.76273</v>
+        <v>-4.76273</v>
       </c>
       <c r="S309" s="5" t="n">
-        <v>6.102016</v>
+        <v>-6.102016</v>
       </c>
       <c r="T309" s="5" t="n">
-        <v>2.588983</v>
+        <v>-2.588983</v>
       </c>
       <c r="U309" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MUR.xlsx
+++ b/output/pdf_financials_xlsx/MUR.xlsx
@@ -1075,28 +1075,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08243</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027353</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011709</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010321</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003571</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037344</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011306</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000364</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1104,31 +1104,31 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010601</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02507</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007732</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003347</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004958</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.062003</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047538</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025252</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017097</v>
       </c>
     </row>
     <row r="13">
@@ -2036,29 +2036,23 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>134.045538</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>141.861723</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>16.055119</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>17.82305</v>
+        <v>18.186256</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>26.505533</v>
+        <v>30.862224</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-97.816417</v>
+        <v>37.530427</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-117.734767</v>
@@ -2110,28 +2104,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.916191</v>
+        <v>-3.998621</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.057751</v>
+        <v>-2.085104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.533367</v>
+        <v>-1.545076</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.138766</v>
+        <v>-2.149087</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.802955</v>
+        <v>-0.806526</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.218344</v>
+        <v>6.255688</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.639516</v>
+        <v>3.650822</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.874897</v>
+        <v>0.875261</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2139,31 +2133,31 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.179806</v>
+        <v>-1.169205</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.590596</v>
+        <v>-2.565526</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.470586</v>
+        <v>-1.462854</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.106105</v>
+        <v>-2.102758</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.76273</v>
+        <v>-4.757772</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.102016</v>
+        <v>-6.040013</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.588983</v>
+        <v>-2.541445</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.927307</v>
+        <v>-1.902055</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-1.82697</v>
+        <v>-1.809873</v>
       </c>
     </row>
     <row r="28">
@@ -2236,28 +2230,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.916191</v>
+        <v>-3.998621</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.057751</v>
+        <v>-2.085104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.533367</v>
+        <v>-1.545076</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.138766</v>
+        <v>-2.149087</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.802955</v>
+        <v>-0.806526</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.218344</v>
+        <v>6.255688</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.639516</v>
+        <v>3.650822</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.874897</v>
+        <v>0.875261</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2265,31 +2259,31 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.179806</v>
+        <v>-1.169205</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.590596</v>
+        <v>-2.565526</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.470586</v>
+        <v>-1.462854</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.106105</v>
+        <v>-2.102758</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.76273</v>
+        <v>-4.757772</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.102016</v>
+        <v>-6.040013</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.588983</v>
+        <v>-2.541445</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.927307</v>
+        <v>-1.902055</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-1.82697</v>
+        <v>-1.809873</v>
       </c>
     </row>
     <row r="30">
@@ -2584,37 +2578,37 @@
         <v>0.567792</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.124168</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.147235</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.39494</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.176697</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.434347</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.062411</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.792033</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.706952</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.823972</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.718166</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.056738</v>
       </c>
     </row>
     <row r="35">
@@ -2706,37 +2700,37 @@
         <v>0.567792</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.124168</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.147235</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.39494</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.176697</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.434347</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.062411</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.792033</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.706952</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.823972</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.718166</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>1.056738</v>
       </c>
     </row>
     <row r="37">
@@ -3438,37 +3432,37 @@
         <v>0.085676</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.183494</v>
+        <v>0.059326</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.383774</v>
+        <v>0.236539</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.434186</v>
+        <v>0.039246</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.337356</v>
+        <v>0.160659</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.598534</v>
+        <v>0.164187</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.153334</v>
+        <v>0.090923</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.111429</v>
+        <v>0.319396</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.577467</v>
+        <v>0.870515</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.217467</v>
+        <v>0.393495</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.7896260000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.117618</v>
+        <v>0.06088</v>
       </c>
     </row>
     <row r="49">
@@ -9068,7 +9062,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14146,7 +14140,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -37238,7 +37232,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -48972,7 +48966,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" s="5" t="n">
@@ -51096,7 +51090,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -51830,7 +51824,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -56314,7 +56308,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E458" s="5" t="n">

--- a/output/pdf_financials_xlsx/MUR.xlsx
+++ b/output/pdf_financials_xlsx/MUR.xlsx
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.010005</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.009717</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.007624</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.002218</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2236,16 +2236,16 @@
         <v>-2.085104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.545076</v>
+        <v>-1.535071</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.149087</v>
+        <v>-2.13937</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.806526</v>
+        <v>-0.798902</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.255688</v>
+        <v>6.257906</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>3.650822</v>
@@ -6619,16 +6619,16 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.010005</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.009717</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.007624</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.002218</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -7384,10 +7384,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.004581</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.09444</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.187182</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -24538,7 +24538,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -27278,7 +27282,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -49844,7 +49852,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
